--- a/artfynd/A 9975-2024 artfynd.xlsx
+++ b/artfynd/A 9975-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115204250</v>
+        <v>115404717</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fridekulla (Fridekulla), Sm</t>
+          <t>A 9975, Valstad, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588559</v>
+        <v>588510</v>
       </c>
       <c r="R2" t="n">
-        <v>6400518</v>
+        <v>6400303</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,37 +765,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115204756</v>
+        <v>115202841</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -830,24 +813,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fridekulla (Fridekulla), Sm</t>
+          <t>Fridekulla, Fridekulla, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588512</v>
+        <v>588403</v>
       </c>
       <c r="R3" t="n">
-        <v>6400481</v>
+        <v>6400312</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,64 +891,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115204115</v>
+        <v>115204756</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fridekulla (Fridekulla), Sm</t>
+          <t>Fridekulla, Fridekulla, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588559</v>
+        <v>588512</v>
       </c>
       <c r="R4" t="n">
-        <v>6400512</v>
+        <v>6400481</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1002,7 +966,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +976,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,19 +1003,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115202841</v>
+        <v>115404944</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1073,19 +1032,27 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fridekulla (Fridekulla), Sm</t>
+          <t>A 9975, Valstad, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588403</v>
+        <v>588480</v>
       </c>
       <c r="R5" t="n">
-        <v>6400312</v>
+        <v>6400487</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,22 +1076,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:46</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:46</t>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,65 +1101,72 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115204366</v>
+        <v>121937252</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fridekulla (Fridekulla), Sm</t>
+          <t>Valstad kvarn, Verkbäck, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588574</v>
+        <v>588563</v>
       </c>
       <c r="R6" t="n">
-        <v>6400508</v>
+        <v>6400291</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,22 +1190,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2025-01-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2025-01-05</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,73 +1220,72 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Stefan Westberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Stefan Westberg, Ingrid Westberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115235517</v>
+        <v>108509206</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 9975, Valstad, Sm</t>
+          <t>Valstad kvarn, Verkbäck, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>588563</v>
       </c>
       <c r="R7" t="n">
-        <v>6400500</v>
+        <v>6400291</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,12 +1309,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,81 +1333,75 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Westberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Stefan Westberg, Ingrid Westberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115405066</v>
+        <v>121937294</v>
       </c>
       <c r="B8" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 9975, Valstad, Sm</t>
+          <t>Valstad kvarn, Verkbäck, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588562</v>
+        <v>588563</v>
       </c>
       <c r="R8" t="n">
-        <v>6400490</v>
+        <v>6400291</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1456,12 +1428,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2025-01-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2025-01-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,27 +1458,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Westberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Westberg, Ingrid Westberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115404717</v>
+        <v>115405066</v>
       </c>
       <c r="B9" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,21 +1481,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1526,12 +1503,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1539,13 +1517,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588510</v>
+        <v>588562</v>
       </c>
       <c r="R9" t="n">
-        <v>6400303</v>
+        <v>6400490</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1583,7 +1561,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1599,6 +1576,2054 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>115204115</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fridekulla, Fridekulla, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>588559</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6400512</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>115204250</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fridekulla, Fridekulla, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>588559</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6400518</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>115204366</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fridekulla, Fridekulla, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>588574</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6400508</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>115235492</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 9975, Valstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>588559</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6400529</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>115235517</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 9975, Valstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>588563</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6400500</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>115404745</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 9975, Valstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>588397</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6400382</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>115404765</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 9975, Valstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>588414</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6400381</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>115404786</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 9975, Valstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>588432</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6400447</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>115404808</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 9975, Valstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>588424</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6400435</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>115404823</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 9975, Valstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>588417</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6400454</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>115404869</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 9975, Valstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>588413</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6400430</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>115404879</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 9975, Valstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>588418</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6400441</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>115404889</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 9975, Valstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>588412</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6400407</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>115404907</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A 9975, Valstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>588438</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6400452</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123780640</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>A 9975, Valstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>588430</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6400445</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123780657</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>A 9975, Valstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>588433</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6400439</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123780694</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>A 9975, Valstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>588437</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6400441</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>123780714</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>A 9975, Valstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>588443</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6400464</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>123780744</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>A 9975, Valstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>588448</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6400479</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
